--- a/artfynd/A 47362-2022 artfynd.xlsx
+++ b/artfynd/A 47362-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47362-2022 artfynd.xlsx
+++ b/artfynd/A 47362-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1983433</v>
+        <v>399536</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691934.9970396959</v>
+        <v>691918</v>
       </c>
       <c r="R2" t="n">
-        <v>7213576.22734286</v>
+        <v>7213575</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2011-10-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-10-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>400117</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691934.9970396959</v>
+        <v>691935</v>
       </c>
       <c r="R3" t="n">
-        <v>7213576.22734286</v>
+        <v>7213576</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,19 +840,9 @@
           <t>2011-10-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-10-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,6 +866,394 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1983431</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Oxberget, Brinkknöreln, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>691869</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7213604</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2011-10-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2011-10-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1983432</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Oxberget, Brinkknöreln, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>691898</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7213578</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2011-10-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2011-10-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1983433</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Oxberget, Brinkknöreln, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>691935</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7213576</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2011-10-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2011-10-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2067981</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Oxberget, Brinkknöreln, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>691869</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7213604</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2011-10-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2011-10-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
